--- a/credentials/Credentials_BCF.xlsx
+++ b/credentials/Credentials_BCF.xlsx
@@ -397,13 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
-  <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="35.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:E7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,6 +412,9 @@
       <c r="D1" t="str">
         <v>Password</v>
       </c>
+      <c r="E1" t="str">
+        <v>Email</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -432,6 +429,9 @@
       <c r="D2" t="str">
         <v>123456</v>
       </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -446,6 +446,9 @@
       <c r="D3" t="str">
         <v>123456</v>
       </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -460,6 +463,9 @@
       <c r="D4" t="str">
         <v>123456</v>
       </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -474,6 +480,9 @@
       <c r="D5" t="str">
         <v>123456</v>
       </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -488,6 +497,9 @@
       <c r="D6" t="str">
         <v>123456</v>
       </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -502,10 +514,13 @@
       <c r="D7" t="str">
         <v>123456</v>
       </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/credentials/Credentials_BCF.xlsx
+++ b/credentials/Credentials_BCF.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -416,111 +416,9 @@
         <v>Email</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Admin 2 BCF</v>
-      </c>
-      <c r="C2" t="str">
-        <v>admin2.bcf</v>
-      </c>
-      <c r="D2" t="str">
-        <v>123456</v>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Admin BCF</v>
-      </c>
-      <c r="C3" t="str">
-        <v>admin.bcf</v>
-      </c>
-      <c r="D3" t="str">
-        <v>123456</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Admin BCF 1</v>
-      </c>
-      <c r="C4" t="str">
-        <v>admin.bcf.1</v>
-      </c>
-      <c r="D4" t="str">
-        <v>123456</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Admin BCF 2</v>
-      </c>
-      <c r="C5" t="str">
-        <v>admin.bcf.2</v>
-      </c>
-      <c r="D5" t="str">
-        <v>123456</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Siswa BCF</v>
-      </c>
-      <c r="C6" t="str">
-        <v>user.bcf</v>
-      </c>
-      <c r="D6" t="str">
-        <v>123456</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Siswa Biasa BCF</v>
-      </c>
-      <c r="C7" t="str">
-        <v>siswa.bcf</v>
-      </c>
-      <c r="D7" t="str">
-        <v>123456</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E1"/>
   </ignoredErrors>
 </worksheet>
 </file>